--- a/BOM/blackbody_c.xlsx
+++ b/BOM/blackbody_c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanya\Documents\LHR\blackbodies v1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49A1BB1-3C7B-446E-82A7-890A55E6FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3826E3-777E-4111-942F-CC3C704EF5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{0D2AC510-AFCC-4373-AA45-728D373DF118}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{0D2AC510-AFCC-4373-AA45-728D373DF118}"/>
   </bookViews>
   <sheets>
     <sheet name="Full BOM" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>Reference</t>
-  </si>
-  <si>
-    <t>Qty</t>
   </si>
   <si>
     <t>PN</t>
@@ -1036,32 +1033,32 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>100</v>
@@ -1070,189 +1067,189 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>25</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
         <v>29</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1262,150 +1259,152 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20279335-D5F0-4F29-B5DF-0B3F99FF3D6E}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="23.3984375" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" customWidth="1"/>
+    <col min="3" max="3" width="18.73046875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
